--- a/tools/config-xlsx/inlay.xlsx
+++ b/tools/config-xlsx/inlay.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:F6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -417,6 +417,9 @@
       <c r="E1" t="str">
         <v>maxLevel</v>
       </c>
+      <c r="F1" t="str">
+        <v>levelRatio</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -429,10 +432,13 @@
         <v>atk</v>
       </c>
       <c r="D2">
-        <v>30</v>
+        <v>33.4</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="F2">
+        <v>1.6</v>
       </c>
     </row>
     <row r="3">
@@ -446,10 +452,13 @@
         <v>hp</v>
       </c>
       <c r="D3">
-        <v>120</v>
+        <v>133.7</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="F3">
+        <v>1.6</v>
       </c>
     </row>
     <row r="4">
@@ -463,10 +472,13 @@
         <v>def</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>8.9</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>1.6</v>
       </c>
     </row>
     <row r="5">
@@ -483,7 +495,10 @@
         <v>0.02</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="F5">
+        <v>1.6</v>
       </c>
     </row>
     <row r="6">
@@ -500,12 +515,15 @@
         <v>0.03</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="F6">
+        <v>1.6</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F6"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -589,7 +607,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -607,10 +625,10 @@
         <v>atk</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="C2">
-        <v>40</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3">
@@ -618,10 +636,10 @@
         <v>hp</v>
       </c>
       <c r="B3">
-        <v>60</v>
+        <v>312</v>
       </c>
       <c r="C3">
-        <v>200</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="4">
@@ -629,10 +647,10 @@
         <v>def</v>
       </c>
       <c r="B4">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="C4">
-        <v>10</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5">
@@ -679,9 +697,86 @@
         <v>0.05</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>atkPct</v>
+      </c>
+      <c r="B9">
+        <v>0.104</v>
+      </c>
+      <c r="C9">
+        <v>0.3119</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>hpPct</v>
+      </c>
+      <c r="B10">
+        <v>0.104</v>
+      </c>
+      <c r="C10">
+        <v>0.3119</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>defPct</v>
+      </c>
+      <c r="B11">
+        <v>0.104</v>
+      </c>
+      <c r="C11">
+        <v>0.3119</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>moveSpeedPct</v>
+      </c>
+      <c r="B12">
+        <v>0.104</v>
+      </c>
+      <c r="C12">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>singleDmgBonus</v>
+      </c>
+      <c r="B13">
+        <v>0.02</v>
+      </c>
+      <c r="C13">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>aoeDmgBonus</v>
+      </c>
+      <c r="B14">
+        <v>0.02</v>
+      </c>
+      <c r="C14">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>skillHaste</v>
+      </c>
+      <c r="B15">
+        <v>0.03</v>
+      </c>
+      <c r="C15">
+        <v>0.08</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C15"/>
   </ignoredErrors>
 </worksheet>
 </file>